--- a/datasets/swarm_poc_results.xlsx
+++ b/datasets/swarm_poc_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\John\Documents\AI_Malware_Reserch\swarm-poc\datasets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED6504B4-EFF1-4F47-9CE6-4EB8ED5D9DAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9A7CE56-0F7B-494A-8A74-FA8CD6D12733}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
